--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SalerRewPenaInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SalerRewPenaInfo.xlsx
@@ -165,7 +165,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -178,8 +178,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -272,13 +278,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -298,14 +317,23 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -611,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="8" customWidth="1"/>
@@ -627,42 +655,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="12" t="s">
         <v>11</v>
       </c>
+    </row>
+    <row r="2" spans="1:12" s="14" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -712,10 +754,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="11"/>
+      <c r="B1" s="10"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
@@ -736,10 +778,10 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="11"/>
+      <c r="B5" s="10"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="1"/>
